--- a/moduli_aziende/aifecs/moduli_compilati/MOD-610-B-Risk_Management.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-610-B-Risk_Management.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra381d6b8d0d64304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3b5130135afa4440"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -488,11 +471,9 @@
         <x:v>SOC / QUAL</x:v>
       </x:c>
       <x:c r="M2" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N2" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N2" s="9"/>
       <x:c r="O2" s="9"/>
       <x:c r="P2" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G2),ISNUMBER(K2)),G2-K2,"")</x:f>
@@ -526,11 +507,9 @@
         <x:v>DID</x:v>
       </x:c>
       <x:c r="M3" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N3" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N3" s="9"/>
       <x:c r="O3" s="9"/>
       <x:c r="P3" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G3),ISNUMBER(K3)),G3-K3,"")</x:f>
@@ -564,11 +543,9 @@
         <x:v>DID</x:v>
       </x:c>
       <x:c r="M4" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N4" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N4" s="9"/>
       <x:c r="O4" s="9"/>
       <x:c r="P4" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G4),ISNUMBER(K4)),G4-K4,"")</x:f>
@@ -602,11 +579,9 @@
         <x:v>IT</x:v>
       </x:c>
       <x:c r="M5" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N5" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N5" s="9"/>
       <x:c r="O5" s="9"/>
       <x:c r="P5" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G5),ISNUMBER(K5)),G5-K5,"")</x:f>
@@ -640,11 +615,9 @@
         <x:v>SEG / TUT</x:v>
       </x:c>
       <x:c r="M6" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N6" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N6" s="9"/>
       <x:c r="O6" s="9"/>
       <x:c r="P6" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G6),ISNUMBER(K6)),G6-K6,"")</x:f>
@@ -678,11 +651,9 @@
         <x:v>DOC / DID</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N7" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N7" s="9"/>
       <x:c r="O7" s="9"/>
       <x:c r="P7" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G7),ISNUMBER(K7)),G7-K7,"")</x:f>
@@ -716,11 +687,9 @@
         <x:v>SEG / DID</x:v>
       </x:c>
       <x:c r="M8" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N8" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N8" s="9"/>
       <x:c r="O8" s="9"/>
       <x:c r="P8" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G8),ISNUMBER(K8)),G8-K8,"")</x:f>
@@ -754,11 +723,9 @@
         <x:v>DID / QUAL</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N9" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N9" s="9"/>
       <x:c r="O9" s="9"/>
       <x:c r="P9" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G9),ISNUMBER(K9)),G9-K9,"")</x:f>
@@ -792,11 +759,9 @@
         <x:v>IT / DIR</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N10" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N10" s="9"/>
       <x:c r="O10" s="9"/>
       <x:c r="P10" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G10),ISNUMBER(K10)),G10-K10,"")</x:f>
@@ -830,11 +795,9 @@
         <x:v>CTR / DID</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N11" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N11" s="9"/>
       <x:c r="O11" s="9"/>
       <x:c r="P11" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G11),ISNUMBER(K11)),G11-K11,"")</x:f>
@@ -868,11 +831,9 @@
         <x:v>SEG / DIR</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N12" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N12" s="9"/>
       <x:c r="O12" s="9"/>
       <x:c r="P12" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G12),ISNUMBER(K12)),G12-K12,"")</x:f>
@@ -906,11 +867,9 @@
         <x:v>SOC</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N13" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N13" s="9"/>
       <x:c r="O13" s="9"/>
       <x:c r="P13" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G13),ISNUMBER(K13)),G13-K13,"")</x:f>
@@ -944,11 +903,9 @@
         <x:v>DIR / CTR / IT</x:v>
       </x:c>
       <x:c r="M14" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N14" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N14" s="9"/>
       <x:c r="O14" s="9"/>
       <x:c r="P14" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G14),ISNUMBER(K14)),G14-K14,"")</x:f>
@@ -982,11 +939,9 @@
         <x:v>QUAL / SOC</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N15" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N15" s="9"/>
       <x:c r="O15" s="9"/>
       <x:c r="P15" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G15),ISNUMBER(K15)),G15-K15,"")</x:f>
@@ -1020,11 +975,9 @@
         <x:v>AMM / DID / IT</x:v>
       </x:c>
       <x:c r="M16" s="9" t="str">
-        <x:v>Scala e soglie da approvare</x:v>
-      </x:c>
-      <x:c r="N16" s="9" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+        <x:v>Scala e soglie da definire</x:v>
+      </x:c>
+      <x:c r="N16" s="9"/>
       <x:c r="O16" s="9"/>
       <x:c r="P16" s="9" t="str">
         <x:f>IF(AND(ISNUMBER(G16),ISNUMBER(K16)),G16-K16,"")</x:f>
@@ -1122,6 +1075,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912644ac9428499c"/>
 </x:worksheet>
 </file>